--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_all_temperatures.xlsx
@@ -485,15 +485,9 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24.2</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -509,13 +503,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>24.3</v>
+        <v>24.8</v>
       </c>
       <c r="E3" t="n">
         <v>18.6</v>
       </c>
       <c r="F3" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -558,7 +552,7 @@
         <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F5" t="n">
         <v>25</v>
@@ -577,15 +571,9 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>26.2</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -600,15 +588,9 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>24.3</v>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -624,10 +606,10 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="E8" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="F8" t="n">
         <v>23.9</v>
@@ -647,10 +629,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="E9" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="F9" t="n">
         <v>25.5</v>
@@ -673,10 +655,10 @@
         <v>32.5</v>
       </c>
       <c r="E10" t="n">
-        <v>19.6</v>
+        <v>12.6</v>
       </c>
       <c r="F10" t="n">
-        <v>26.1</v>
+        <v>22.6</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -692,15 +674,9 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -715,15 +691,9 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>19</v>
-      </c>
-      <c r="F12" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -782,10 +752,10 @@
         <v>30.8</v>
       </c>
       <c r="E15" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="F15" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -801,15 +771,9 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -824,15 +788,9 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E17" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="F17" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -891,10 +849,10 @@
         <v>28.2</v>
       </c>
       <c r="E20" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="F20" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -910,15 +868,9 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>25</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -933,14 +885,10 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="n">
-        <v>30</v>
-      </c>
-      <c r="E22" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -979,14 +927,10 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>19.8</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>26.7</v>
+        <v>26.2</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1003,13 +947,13 @@
         <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>30.4</v>
+        <v>24.7</v>
       </c>
       <c r="E25" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="F25" t="n">
-        <v>25.3</v>
+        <v>22.6</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1026,13 +970,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>24.7</v>
+        <v>28.6</v>
       </c>
       <c r="E26" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
-        <v>22.6</v>
+        <v>24.8</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1049,13 +993,13 @@
         <v>26</v>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>31.9</v>
       </c>
       <c r="E27" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="F27" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1071,9 +1015,15 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22.1</v>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1089,13 +1039,13 @@
         <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>24</v>
+        <v>29.4</v>
       </c>
       <c r="E29" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="F29" t="n">
-        <v>22.1</v>
+        <v>24.5</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1112,13 +1062,13 @@
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>29.5</v>
+        <v>37.8</v>
       </c>
       <c r="E30" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1135,13 +1085,13 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>18.6</v>
       </c>
       <c r="F31" t="n">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1158,13 +1108,13 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="E32" t="n">
-        <v>18.6</v>
+        <v>23.5</v>
       </c>
       <c r="F32" t="n">
-        <v>25.3</v>
+        <v>20.9</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_all_temperatures.xlsx
@@ -503,13 +503,13 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="E3" t="n">
         <v>18.6</v>
       </c>
       <c r="F3" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -548,15 +548,9 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="n">
-        <v>33</v>
-      </c>
-      <c r="E5" t="n">
-        <v>17</v>
-      </c>
-      <c r="F5" t="n">
-        <v>25</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -571,9 +565,15 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26.2</v>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -588,9 +588,15 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24.3</v>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -606,10 +612,10 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="E8" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="F8" t="n">
         <v>23.9</v>
@@ -629,10 +635,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="E9" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="F9" t="n">
         <v>25.5</v>
@@ -655,10 +661,10 @@
         <v>32.5</v>
       </c>
       <c r="E10" t="n">
-        <v>12.6</v>
+        <v>19.6</v>
       </c>
       <c r="F10" t="n">
-        <v>22.6</v>
+        <v>26.1</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -674,9 +680,15 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -691,9 +703,15 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -709,13 +727,13 @@
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="E13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="F13" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -731,9 +749,15 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23.5</v>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -752,10 +776,10 @@
         <v>30.8</v>
       </c>
       <c r="E15" t="n">
-        <v>17.8</v>
+        <v>18.4</v>
       </c>
       <c r="F15" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -771,9 +795,15 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24.5</v>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -788,9 +818,15 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>25.7</v>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -805,9 +841,15 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24.7</v>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -823,13 +865,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>30.8</v>
+        <v>28.2</v>
       </c>
       <c r="E19" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="F19" t="n">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -846,13 +888,13 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>28.2</v>
+        <v>29.8</v>
       </c>
       <c r="E20" t="n">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
       <c r="F20" t="n">
-        <v>23.9</v>
+        <v>25</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -868,9 +910,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -885,10 +933,14 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>20.2</v>
+      </c>
       <c r="F22" t="n">
-        <v>24.8</v>
+        <v>26.5</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
@@ -905,13 +957,13 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>32.8</v>
+        <v>33.6</v>
       </c>
       <c r="E23" t="n">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="F23" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -927,10 +979,14 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20.2</v>
+      </c>
       <c r="F24" t="n">
-        <v>26.2</v>
+        <v>25.3</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -973,10 +1029,10 @@
         <v>28.6</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1016,10 +1072,10 @@
         <v>27</v>
       </c>
       <c r="D28" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="E28" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="F28" t="n">
         <v>22.1</v>
@@ -1039,13 +1095,13 @@
         <v>28</v>
       </c>
       <c r="D29" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="E29" t="n">
         <v>19.6</v>
       </c>
       <c r="F29" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1062,10 +1118,10 @@
         <v>29</v>
       </c>
       <c r="D30" t="n">
-        <v>37.8</v>
+        <v>32.8</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F30" t="n">
         <v>24.9</v>
@@ -1085,13 +1141,13 @@
         <v>30</v>
       </c>
       <c r="D31" t="n">
-        <v>32.2</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
         <v>18.6</v>
       </c>
       <c r="F31" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1108,13 +1164,13 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>18</v>
+        <v>23.8</v>
       </c>
       <c r="E32" t="n">
-        <v>23.5</v>
+        <v>19</v>
       </c>
       <c r="F32" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_all_temperatures.xlsx
@@ -485,9 +485,15 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>24.2</v>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -506,7 +512,7 @@
         <v>24.3</v>
       </c>
       <c r="E3" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F3" t="n">
         <v>21.5</v>
@@ -548,9 +554,15 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>33</v>
+      </c>
+      <c r="E5" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" t="n">
+        <v>25</v>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -612,7 +624,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="E8" t="n">
         <v>19.6</v>
@@ -635,10 +647,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="E9" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="F9" t="n">
         <v>25.5</v>
@@ -658,10 +670,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="E10" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="F10" t="n">
         <v>26.1</v>
@@ -684,7 +696,7 @@
         <v>29.5</v>
       </c>
       <c r="E11" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="F11" t="n">
         <v>24.9</v>
@@ -703,15 +715,9 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="D12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>19</v>
-      </c>
-      <c r="F12" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
@@ -726,15 +732,9 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="E13" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F13" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -749,15 +749,9 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F14" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -819,13 +813,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>32.1</v>
+        <v>21.5</v>
       </c>
       <c r="E17" t="n">
-        <v>19.3</v>
+        <v>19.9</v>
       </c>
       <c r="F17" t="n">
-        <v>25.7</v>
+        <v>20.7</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -864,15 +858,9 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F19" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -887,15 +875,9 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>25</v>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -910,15 +892,9 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>24.9</v>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -933,15 +909,11 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="n">
-        <v>32.8</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>20.2</v>
       </c>
-      <c r="F22" t="n">
-        <v>26.5</v>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -956,15 +928,11 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="n">
-        <v>33.6</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F23" t="n">
-        <v>26.8</v>
-      </c>
+        <v>19.8</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -1026,13 +994,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>28.6</v>
+        <v>38.6</v>
       </c>
       <c r="E26" t="n">
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>24.3</v>
+        <v>29.3</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1052,10 +1020,10 @@
         <v>31.9</v>
       </c>
       <c r="E27" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="F27" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1071,15 +1039,9 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="n">
-        <v>24</v>
-      </c>
-      <c r="E28" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1094,14 +1056,10 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E29" t="n">
-        <v>19.6</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>24.4</v>
+        <v>34.5</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
@@ -1164,10 +1122,10 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="E32" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="F32" t="n">
         <v>21.4</v>

--- a/results/04_final_refined_daily_hydroclimate_data/209/Daily_all_temperatures.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/209/Daily_all_temperatures.xlsx
@@ -509,7 +509,7 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="n">
         <v>18.7</v>
@@ -624,7 +624,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="E8" t="n">
         <v>19.6</v>
@@ -647,10 +647,10 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="E9" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="F9" t="n">
         <v>25.5</v>
@@ -670,10 +670,10 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="E10" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="F10" t="n">
         <v>26.1</v>
@@ -696,7 +696,7 @@
         <v>29.5</v>
       </c>
       <c r="E11" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="F11" t="n">
         <v>24.9</v>
@@ -732,9 +732,15 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25.4</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -749,9 +755,15 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F14" t="n">
+        <v>23.5</v>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -789,15 +801,9 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="D16" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E16" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F16" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -813,13 +819,13 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>21.5</v>
+        <v>32.1</v>
       </c>
       <c r="E17" t="n">
-        <v>19.9</v>
+        <v>19.3</v>
       </c>
       <c r="F17" t="n">
-        <v>20.7</v>
+        <v>25.7</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -858,9 +864,15 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F19" t="n">
+        <v>23.8</v>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -875,9 +887,15 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>25</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -892,9 +910,15 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>24.9</v>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -909,11 +933,15 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>37.6</v>
+      </c>
       <c r="E22" t="n">
         <v>20.2</v>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>28.9</v>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -928,11 +956,15 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>33.6</v>
+      </c>
       <c r="E23" t="n">
         <v>19.8</v>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>26.7</v>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -994,13 +1026,13 @@
         <v>25</v>
       </c>
       <c r="D26" t="n">
-        <v>38.6</v>
+        <v>28.6</v>
       </c>
       <c r="E26" t="n">
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>29.3</v>
+        <v>24.3</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1020,10 +1052,10 @@
         <v>31.9</v>
       </c>
       <c r="E27" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="F27" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1039,9 +1071,15 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E28" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>22.1</v>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -1056,10 +1094,14 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19.5</v>
+      </c>
       <c r="F29" t="n">
-        <v>34.5</v>
+        <v>24.5</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
